--- a/大會師總戰報_20260616/🎨_全策略大會師總表_20260616.xlsx
+++ b/大會師總戰報_20260616/🎨_全策略大會師總表_20260616.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,12 +478,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2379.TW</t>
+          <t>6166.TW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>678</v>
+        <v>141</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F2" t="n">
-        <v>4254</v>
+        <v>3624</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -509,12 +509,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2347.TW</t>
+          <t>4721.TWO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>美琪瑪</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -523,13 +523,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="F3" t="n">
-        <v>7038</v>
+        <v>4601</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -540,12 +540,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3003.TW</t>
+          <t>6788.TWO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>健和興</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67.40000000000001</v>
+        <v>449</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>4806</v>
+        <v>1965</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -571,12 +571,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2867.TW</t>
+          <t>4976.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>三商壽</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8.529999999999999</v>
+        <v>34.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="F5" t="n">
-        <v>37888</v>
+        <v>2908</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -602,12 +602,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5880.TW</t>
+          <t>3093.TWO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>港建*</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.6</v>
+        <v>64.7</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="F6" t="n">
-        <v>41277</v>
+        <v>3440</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -633,58 +633,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6180.TWO</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>橘子</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>回後買上漲_嚴格版(1+2+3) | 回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48.3</v>
+        <v>4470</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="F7" t="n">
-        <v>3389</v>
+        <v>10400</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6179.TWO</t>
+          <t>1563.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>亞通</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>四均線起漲精選 | 回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.3</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="n">
-        <v>4043</v>
+        <v>1142</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -695,27 +695,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4904.TW</t>
+          <t>3149.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>正達</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>112.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F9" t="n">
-        <v>13212</v>
+        <v>4095</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -726,27 +726,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2882.TW</t>
+          <t>3311.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>閎暉</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>109.5</v>
+        <v>41.3</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2</v>
+        <v>8.4</v>
       </c>
       <c r="F10" t="n">
-        <v>54267</v>
+        <v>3897</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -757,167 +757,167 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>5426.TWO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>振發</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>回後買上漲_標準版(1+2) | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2520</v>
+        <v>35.6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="F11" t="n">
-        <v>3068</v>
+        <v>2980</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2348.TW</t>
+          <t>2405.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>海悅</t>
+          <t>輔信</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>74.59999999999999</v>
+        <v>19.45</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="F12" t="n">
-        <v>1223</v>
+        <v>4275</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1907.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>永豐餘</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.95</v>
+        <v>960</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>3470</v>
+        <v>15473</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>6191.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 四均線起漲精選</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>26.9</v>
+        <v>103</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>6.9</v>
       </c>
       <c r="F14" t="n">
-        <v>15308</v>
+        <v>21025</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1312.TW</t>
+          <t>9933.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>中鼎</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選 | 回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.15</v>
+        <v>42.8</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="F15" t="n">
-        <v>13800</v>
+        <v>7999</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1905.TW</t>
+          <t>0055.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>華紙</t>
+          <t>元大MSCI金融</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.15</v>
+        <v>41</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="n">
-        <v>14948</v>
+        <v>941</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -943,27 +943,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2399.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>映泰</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52.8</v>
+        <v>53.9</v>
       </c>
       <c r="E17" t="n">
         <v>1.8</v>
       </c>
       <c r="F17" t="n">
-        <v>14011</v>
+        <v>10031</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -974,12 +974,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2892.TW</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31.8</v>
+        <v>159</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F18" t="n">
-        <v>50724</v>
+        <v>26842</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1005,12 +1005,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3147.TWO</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>350</v>
+        <v>2375</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="n">
-        <v>527</v>
+        <v>25573</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1036,27 +1036,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>2375.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>凱美</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>876</v>
+        <v>189.5</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="F20" t="n">
-        <v>4635</v>
+        <v>13207</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1067,27 +1067,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3290.TWO</t>
+          <t>2419.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>東浦</t>
+          <t>仲琦</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>29.75</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>3939</v>
+        <v>2221</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2633.TW</t>
+          <t>2428.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台灣高鐵</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26.15</v>
+        <v>310</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="F22" t="n">
-        <v>17800</v>
+        <v>3268</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -1129,12 +1129,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2455.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>405.5</v>
+        <v>61.6</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>17707</v>
+        <v>30851</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1160,12 +1160,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2884.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>35.2</v>
+        <v>105.25</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="F24" t="n">
-        <v>59482</v>
+        <v>95906</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1191,12 +1191,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2412.TW</t>
+          <t>1809.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>中釉</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>146.5</v>
+        <v>51.5</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F25" t="n">
-        <v>12835</v>
+        <v>6617</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1222,27 +1222,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3520.TWO</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>華盈</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ABC突破切線精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17.05</v>
+        <v>141.5</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F26" t="n">
-        <v>1620</v>
+        <v>325943</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1253,27 +1253,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3466.TWO</t>
+          <t>2316.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>德晉</t>
+          <t>楠梓電</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>33.55</v>
+        <v>171.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F27" t="n">
-        <v>1198</v>
+        <v>5586</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1284,27 +1284,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3339.TWO</t>
+          <t>2327.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>49.5</v>
+        <v>940</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F28" t="n">
-        <v>6808</v>
+        <v>39733</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1315,12 +1315,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3293.TWO</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>772</v>
+        <v>55.7</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F29" t="n">
-        <v>1697</v>
+        <v>6392</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1346,12 +1346,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4991.TWO</t>
+          <t>1301.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>587</v>
+        <v>47.25</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>7307</v>
+        <v>36007</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1377,12 +1377,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3550.TW</t>
+          <t>1319.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯穎</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1391,13 +1391,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.85</v>
+        <v>105</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F31" t="n">
-        <v>10936</v>
+        <v>5332</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1408,12 +1408,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6199.TWO</t>
+          <t>1569.TWO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>天品</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1422,13 +1422,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>92.3</v>
+        <v>49.85</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>901</v>
+        <v>938</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -1439,12 +1439,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6446.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>991</v>
+        <v>200.2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F33" t="n">
-        <v>1994</v>
+        <v>13334</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -1470,12 +1470,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6725.TWO</t>
+          <t>3031.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>佰鴻</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>320</v>
+        <v>28.75</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>534</v>
+        <v>700</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1501,12 +1501,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6742.TW</t>
+          <t>3023.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1515,13 +1515,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>61.4</v>
+        <v>319</v>
       </c>
       <c r="E35" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="n">
-        <v>6835</v>
+        <v>948</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1532,27 +1532,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6919.TW</t>
+          <t>3019.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>96.59999999999999</v>
+        <v>158</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F36" t="n">
-        <v>3181</v>
+        <v>16499</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -1563,27 +1563,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7751.TWO</t>
+          <t>2646.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>星宇航空</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>老余裸K_賺賠比精選</t>
+          <t>回後買上漲基礎版</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1445</v>
+        <v>20.6</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>522</v>
+        <v>5954</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -1594,12 +1594,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7777.TWO</t>
+          <t>3008.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>能率亞洲</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1608,13 +1608,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>43.25</v>
+        <v>4420</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="F38" t="n">
-        <v>13158</v>
+        <v>3302</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -1625,27 +1625,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8074.TWO</t>
+          <t>2630.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>亞航</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>老余裸K_賺賠比精選</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>77</v>
+        <v>39.35</v>
       </c>
       <c r="E39" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>4852</v>
+        <v>860</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -1656,12 +1656,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8926.TW</t>
+          <t>2465.TW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>麗臺</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>76.8</v>
+        <v>83</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="F40" t="n">
-        <v>14307</v>
+        <v>2301</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1687,31 +1687,1736 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9940.TW</t>
+          <t>2369.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>信義</t>
+          <t>菱生</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>回後買上漲基礎版</t>
+          <t>ABC突破切線精選</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20.25</v>
+        <v>35.75</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="F41" t="n">
-        <v>963</v>
+        <v>14220</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2441.TW</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>超豐</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>127</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9274</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3114.TWO</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>好德</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F43" t="n">
+        <v>952</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3234.TWO</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>光環</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2782</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3062.TW</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>建漢</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>26</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4371</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3049.TW</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>精金</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>11296</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3081.TWO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2335</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3041.TW</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>揚智</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>27</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5593</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3357.TWO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>臺慶科</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>322</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13925</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3362.TWO</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>先進光</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6849</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3443.TW</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4815</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1033</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3413.TW</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>京鼎</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ABC突破切線精選</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>322</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4434</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3481.TW</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F53" t="n">
+        <v>98818</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3504.TW</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>揚明光</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2302</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3543.TW</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>州巧</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>503</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3450.TW</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>507</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5283</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3596.TW</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>智易</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1901</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3653.TW</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>3835</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1307</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3289.TWO</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>宜特</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>169</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1902</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3260.TWO</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>423</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>16126</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3294.TWO</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>英濟</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2377</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3321.TW</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>同泰</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1812</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3339.TWO</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>泰谷</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>45</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3590</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3044.TW</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>520</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3334</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4760.TWO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>勤凱</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>401.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1546</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4577.TWO</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>達航科技</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>91</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>739</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3717.TW</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>聯嘉投控</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3460</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3707.TWO</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>漢磊</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>14741</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3689.TWO</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1905</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3704.TW</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>合勤控</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4329</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4958.TW</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>590</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>49593</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4919.TW</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>新唐</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>193</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>7773</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>5392.TWO</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>能率</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>6933</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>5289.TWO</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1920</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3524</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4973.TWO</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>廣穎</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>210</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3093</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>6155.TW</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>鈞寶</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F76" t="n">
+        <v>18659</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>6187.TWO</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1130</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3006</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>6207.TWO</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>雷科</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>136</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F78" t="n">
+        <v>7493</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4952.TW</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>凌通</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4808</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4931.TWO</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>新盛力</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>252</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F80" t="n">
+        <v>10267</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>6259.TWO</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>百徽</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2906</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>6220.TWO</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>岳豐</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>37</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2673</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>6584.TWO</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>625</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>556</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>6426.TW</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>統新</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>209</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1274</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>6668.TW</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>中揚光</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>6683.TWO</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>雍智科技</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1585</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1401</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>6719.TW</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>力智</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1447</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>6548.TWO</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>長科*</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2801</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>6862.TW</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>三集瑞-KY</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>202</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>6909.TW</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>創控</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>709</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>8110.TW</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>華東</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>11273</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>6919.TW</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>康霈*</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>老余裸K_賺賠比精選</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4260</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>8215.TW</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>明基材</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F93" t="n">
+        <v>8931</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>8358.TWO</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>624</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1758</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>8936.TWO</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>國統</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>14121</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>8996.TW</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>回後買上漲基礎版</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1386</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
         <v>1</v>
       </c>
     </row>
